--- a/results/qa_assessment.xlsx
+++ b/results/qa_assessment.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK77"/>
+  <dimension ref="A1:AK170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,7 +737,7 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -758,19 +758,19 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Abstract clearly states the research objective (automating process discovery from event data), and explicitly names stochastic techniques (Markov models, algorithmic grammar inference, neural networks). However, no specific SE context is described, no concrete data source is identified, no empirical validation is mentioned, and no quality metrics are reported.</t>
         </is>
       </c>
     </row>
@@ -899,37 +899,37 @@
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objective stated (process recovery method for process improvement). QA2: SE context described (software development organization, project enactment). QA3: Data source not reproducibly specified (only 'organizations' mentioned, no dataset name/details). QA4: No formal PM technique named (mining mentioned but not specific algorithm like alpha miner). QA5: Empirical validation present (pilot case study conducted). QA6: No threats to validity or limitations discussed. QA7: No mention of dataset availability or code release. QA8: No process model quality metrics reported (fitnes</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>1</v>
@@ -1076,19 +1076,19 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clear (effectiveness of process discovery algorithms in software organizations). Software engineering context is stated (process modeling for software process improvement teams). Four process discovery/mining algorithms are formally mentioned. A case study provides empirical validation, and discrepancies/weaknesses are discussed as validity concerns. However, specific data source is not named, no quality metrics (fitness, precision, etc.) are reported, and reproducibility/data availability is not mentioned.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1232,22 +1232,22 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objectives for event-based process analysis in SE (QA1). SE context is detailed: continuous integration and testing processes in development environments (QA2). Data source is described as heterogeneous engineering tools integrated via service-oriented platform (QA3). No specific PM/stochastic technique is formally named (QA4=0). Empirical evaluation is conducted using CI/test process case study (QA5). Limitations and strengths are discussed (QA6). Data/code availability not mentioned (QA7=0). Process quality metrics reported: process structure comparison, perform</t>
         </is>
       </c>
     </row>
@@ -1379,34 +1379,34 @@
         <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (process recovery from artifacts). SE context well-described (version control, bug trackers, mailing lists). Data sources explicitly named (VCS, bug trackers, mailing lists from open source projects). However, no formal PM technique (alpha miner, inductive miner, etc.) is specified; ML/NLP/statistics are mentioned generically. No validity threats discussed. No metrics (fitness, precision, etc.) or reproducibility/code availability mentioned.</t>
         </is>
       </c>
     </row>
@@ -1541,10 +1541,10 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objective of applying process mining to software repositories. SE context is detailed (VCS, bug trackers, mail archives, development process analysis). Data sources are described (multiple software repositories). Process mining technique is formally identified (discovery, ProM framework, FRASR tool). Empirical validation through case studies is mentioned. However, no threats to validity are discussed, reproducibility/data availability is not stated, and no quality metrics (fitness, precision, recall, etc.) are reported.</t>
         </is>
       </c>
     </row>
@@ -1697,34 +1697,34 @@
         <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (explore process discovery via link analysis on FreeBSD repository). SE context (open source development, repository mining) and data source (FreeBSD repository) are identified. However, no specific PM technique is formally named, no quality metrics are reported, reproducibility and validity threats are not discussed.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1815,19 +1815,19 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (applying process mining for conformance checking in SW development); specific SE context (software development process management); reproducible data source (Brazilian software house, 5 years of event logs, 2,000+ cases); formal technique named (process mining, conformance checking). Empirical evaluation on real event logs demonstrated. No threats to validity or quality metrics (fitness, precision, etc.) explicitly discussed; reproducibility resources not mentioned.</t>
         </is>
       </c>
     </row>
@@ -1962,10 +1962,10 @@
         <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective of extracting hidden process information using process mining on real software development logs. SE context (custom software development in automotive IT department), data source (incident records from one release), and technique (ProM Framework with process discovery) are all explicitly named. Empirical application on real event logs is reported. No threats to validity, data availability, or quantitative quality metrics (fitness, precision, etc.) are mentioned.</t>
         </is>
       </c>
     </row>
@@ -2121,31 +2121,31 @@
         <v>1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (process cube for defect resolution analysis); SE context detailed (ITS, PCR, VCS systems); data source reproducible (Google Chromium project); PM technique formally defined (process cube, OLAP operations, process mining perspectives); empirical validation via case study; process mining metrics reported (control flow, time perspective analysis); no explicit discussion of validity threats or data/code availability.</t>
         </is>
       </c>
     </row>
@@ -2280,13 +2280,13 @@
         <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study clearly states objectives (improving goodness of process models via clustering), describes SE context (ITS/Bugzilla for bug lifecycle), names data source (Firefox open-source project event logs), formally defines techniques (K-Medoid with LCS/DTW distance metrics, process map discovery), evaluates empirically on real ITS data, discusses complexity as a limitation/threat, and reports fitness and structural complexity metrics. No mention of code/data availability.</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>1</v>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2451,19 +2451,19 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (develop a process mining platform for project management optimization). SE context is specified (IT company projects, SDLC). Heuristic Miner Algorithm is formally named as the PM technique. However, no empirical validation, specific data source, quality metrics, or reproducibility information is provided—this appears to be a project proposal rather than a completed empirical study.</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>1</v>
@@ -2610,19 +2610,19 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (process discovery, conformance checking, software development analysis). Software engineering context is detailed (IDEs, cloud platforms, developer activities). Process mining techniques are named (discovery, conformance checking). However, no empirical evaluation results, specific data sources, validity threats, reproducibility details, or quality metrics are provided in the abstract—this appears to be a research proposal rather than a completed empirical study.</t>
         </is>
       </c>
     </row>
@@ -2695,13 +2695,13 @@
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2713,19 +2713,19 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives on improving maintenance via process mining and predictive analytics (QA1). Software engineering context explicitly stated as software maintenance process in repositories (QA2). Data sources named: software repositories, open source and commercial projects (QA3). Techniques formally identified: process mining and predictive analytics (QA4). Case studies on real projects confirm empirical validation (QA5). No mention of threats to validity, limitations, or generalizability (QA6). No statement about data/code availability (QA7). No specific quality metrics (fitness, pre</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>1</v>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2872,19 +2872,19 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated: generate and prioritize test cases using process mining from user behavior logs. Software context (testing, test case generation) is described. Process mining is named as the technique. However, no specific data source is identified, no empirical validation is mentioned in the abstract, threats to validity are not discussed, code/data availability is not stated, and no quality metrics are reported.</t>
         </is>
       </c>
     </row>
@@ -3019,10 +3019,10 @@
         <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -3031,19 +3031,19 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Abstract clearly states research goal (formal mapping of Waterfall characteristics to stochastic model for performance prediction). QA2: Waterfall model in software projects is explicitly named as SE context. QA4: Stochastic modeling and simulations are named as techniques. QA3/QA5/QA6/QA7/QA8: No empirical data source, case study, experiments, real data application, threats to validity discussion, reproducibility information, or specific performance metrics (fitness, precision, etc.) are mentioned in the abstract.</t>
         </is>
       </c>
     </row>
@@ -3197,12 +3197,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective (assess Scrum implementation via process mining), describes SE context (Agile/Scrum in IT organization), names data source (Jira Software event logs from two projects), and defines PM technique (workflow discovery and event log analysis). Empirical validation via case study is present, and limitations are discussed (e.g., customer collaboration not detectable). However, no quantitative model quality metrics (fitness, precision, generalization) or formal accuracy measures are reported, and code/data availability is not mentioned.</t>
         </is>
       </c>
     </row>
@@ -3281,31 +3281,31 @@
         <v>1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objective (discovering software behavioral models from execution data), describes SE context (software runtime behavior analysis, method calls), names specific data sources (synthetic and real-life software event logs), formally defines PM technique (hierarchical Petri nets with extended process discovery), validates empirically with synthetic and real-life logs, mentions limitations regarding infrequent behavior, implements in open-source ProM toolkit, and implicitly reports quality through model visualization and applicability demonstration.</t>
         </is>
       </c>
     </row>
@@ -3437,10 +3437,10 @@
         <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Research aim is stated (improve activity management in ERP development using Kanban and process mining). QA2: Software context is described (ERP development, activity/task management). QA3: Data sources are named (Issue Tracking System and Kanban board). QA4: Process mining is mentioned generically but no specific technique is formally defined (e.g., no alpha miner, inductive miner named). QA5: Empirical application described (mapping current process, implementing tools, detecting performance problems). QA6: No discussion of limitations or threats to validity. QA7: No mention of dataset o</t>
         </is>
       </c>
     </row>
@@ -3537,13 +3537,13 @@
         <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3555,19 +3555,19 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective clearly stated (software process analysis methodology for legacy systems). SE context explicitly named (legacy software at ASML, high-tech company). Data source identified (observations from system on the run / event logs from industrial legacy software). However, no specific PM technique formally defined, no validity threats discussed, no reproducibility package mentioned, and no process model quality metrics reported.</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3714,19 +3714,19 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective to evaluate process discovery algorithms in industry. SE context explicitly stated (software engineering company). Real event log from named company used as data source. Process discovery methods formally identified as the technique. Empirical evaluation conducted with domain experts. Quality metrics (understandability, correctness, precision, usefulness) reported. No mention of threats to validity or data/code availability.</t>
         </is>
       </c>
     </row>
@@ -3861,31 +3861,31 @@
         <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI23" t="b">
         <v>1</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective of measuring team efficiency through process discovery and comparison (QA1). SE context explicitly specified: Java programmers, Eclipse IDE, code smells detection task (QA2). Data source reproducible: IDE event logs from independent teams performing specific task (QA3). Process mining techniques named: process model discovery, conformance checking against reference model (QA4). Empirical validation via controlled experiment with multiple teams and expert assessment (QA5). Limitations acknowledged regarding process variability and human factors (QA6). No mention o</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -4032,19 +4032,19 @@
         <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI24" t="b">
         <v>1</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (automatic activity mining from SVN logs). SE context well-described (SCM systems, software development). Data source explicitly named (SVN logs from ArgoUML and jEdit projects, 80,000+ events, 1998-2015). Naive Bayes classifier formally specified as the stochastic technique. Empirical validation on real-world projects. Evaluation metrics reported (precision, recall, F-measure). No availability of code/data or threats to validity discussion mentioned.</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>1</v>
@@ -4182,28 +4182,28 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI25" t="b">
         <v>1</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective: evaluating performance (bottlenecks and fraud) in Agile SDLC using Petri nets (QA1, QA4). SE context is specific: Agile development model (QA2). Empirical evaluation mentioned ('based on experiment') with cluster analysis for fraud detection (QA5, QA8). However, data source is not reproducibly described—no specific projects, repositories, or datasets named (QA3). No dataset/code availability or reproducibility information provided (QA7). Threats to validity not discussed (QA6).</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>1</v>
@@ -4294,19 +4294,19 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Abstract clearly states research aim (investigate Agile methodology for performance analysis and detect bottlenecks/dependencies) and names SE context (Agile development teams). Alpha++ technique is formally identified as the PM method used. However, no specific data source is reproducibly described, no empirical validation results are reported, threats to validity are not discussed, and no dataset/code availability or quality metrics (fitness, precision, etc.) are mentioned.</t>
         </is>
       </c>
     </row>
@@ -4441,31 +4441,31 @@
         <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on coding behavior evaluation via process mining (QA1). SE context explicitly stated: IDE usage logs and software development processes (QA2). Data source clearly identified: IDE event logs from 40 novice developers in 5 sessions (QA3). Technique formally named: conformance checking with process mining (QA4). Empirical evaluation conducted on real developers (QA5). Quality metric reported: behavioral pattern identification and skill-based performance comparison (QA8). No limitations or threats to validity discussed (QA6). Data/code availability not mentioned (QA7).</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4553,22 +4553,22 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI28" t="b">
         <v>1</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objective (understand coding workflow via process mining). SE context explicitly described (IDE usage, CS2 students, coding workflow). Data source named (IDE event logs from CodingMiner environment, 20 students, 4 assignments). Fuzzy miner technique formally identified. Empirical evaluation conducted (case study with 20 students). Process model quality assessed through discovered patterns and behavioral insights. Threats to validity not discussed; data/code availability not mentioned.</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4656,22 +4656,22 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study clearly states research objectives (predicting remaining duration and next activities in issue handling). It specifies the SE context (software development, issue handling, SLA monitoring) and data source (Google Chromium Project event logs). However, no formal stochastic/PM technique is explicitly named (only encoding techniques and prediction methods); threats to validity are not discussed; and data/code availability is not mentioned. Quality metrics (MAE, accuracy) are reported.</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
         <v>1</v>
@@ -4750,7 +4750,7 @@
         <v>1</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective of composing efficient traces via evolutionary computing on event logs (QA1). Software engineering context is process mining on organizational event logs (QA2). Data source explicitly named as BPIC'15 dataset (QA3). Genetic Algorithms formally identified as the stochastic technique (QA4). Empirical validation reported on BPIC'15 with optimality measurements (QA5, QA8). No discussion of threats/limitations or data/code availability mentioned (QA6, QA7).</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI31" t="b">
         <v>1</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (bottleneck detection in agile development). Software engineering context is explicitly named (agile software development process). Data source is described (event logs generated from workflow management systems). Process mining techniques are formally named (Alpha++ Algorithm, Heuristic Miner Algorithm, dotted chart analysis). Empirical validation is present (experiment proving automatic event log creation and bottleneck detection). However, no threats to validity or generalizability limitations are discussed, and no data/code availability is mentioned.</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>6</v>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective of extracting process constraints from issue-tracking data. Software engineering context (issue tracking, development processes) and data source (Jira from four real-world projects) are well described. Constraint mining technique is formally named. Empirical evaluation with domain expert validation is present. Limitations and comparison with official process are discussed. However, no specific quality metrics (fitness, precision, recall, F1) are reported, and code/data availability is not mentioned.</t>
         </is>
       </c>
     </row>
@@ -5171,31 +5171,31 @@
         <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI33" t="b">
         <v>1</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objectives (connecting reliability models to defect tracking); describes SE context (software defect lifecycle management); names data source (NASA project defect tracking database); formally defines stochastic techniques (Markov chain with 13 states, transition probabilities, distributional models); validates empirically with real NASA data; discusses limitations and tradeoffs between approaches; and reports performance metrics comparing predictive and computational measures. No mention of reproducible code/data availability.</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>1</v>
@@ -5342,19 +5342,19 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI34" t="b">
         <v>1</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective to demonstrate hybrid process simulation challenges (QA1). Software context is explicit: software development process simulation with focus on project duration/release date prediction (QA2). Specific simulation techniques are named: System Dynamics and Discrete Event Simulation (QA4). Validation through comparison with actual industrial process enactment demonstrates empirical evaluation (QA5). Limitations and challenges are discussed throughout (QA6). However, no specific data source repository/project details are disclosed (QA3), no open-source artifacts are me</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -5498,22 +5498,22 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI35" t="b">
         <v>1</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (analyze software debugging processes using PM). SE context is specified (IDE debugging, student training). Data source is named (event logs from Microsoft Visual Studio extension). PM technique explicitly identified (ProM platform, conformance checking). Empirical validation evident through toolkit implementation and application. Process quality metrics implied via conformance checking evaluation. No reproducibility details or threats to validity discussion provided.</t>
         </is>
       </c>
     </row>
@@ -5648,10 +5648,10 @@
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5667,12 +5667,12 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (detecting sudden drift in single-instance logs). Software engineering context is specified (software development process logs). Drift detection algorithm and LDA topic model are formally named techniques. Empirical validation is mentioned (multiple simulated datasets evaluated). However, no specific data source is reproducibly described, no availability of code/data is mentioned, and no quality metrics (fitness, precision, etc.) are reported—only general effectiveness claims.</t>
         </is>
       </c>
     </row>
@@ -5804,34 +5804,34 @@
         <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI37" t="b">
         <v>1</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective: characterize CI/CD adoption in repositories. Software context well-described: GitHub repositories, CI/CD practices, development processes. Data source explicitly named: GitHub repositories with execution workflows and metrics extraction. However, no formal process mining or stochastic technique is named (QA4=0), no reproducibility statement about data/code availability (QA7=0), and no quantitative process model quality metrics reported (QA8=0). Threats to validity are not discussed (QA6=0).</t>
         </is>
       </c>
     </row>
@@ -5963,10 +5963,10 @@
         <v>1</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The paper clearly states the research objective (work-item prediction challenge in software engineering workflows). It describes the SE context in detail (developers, incident responders, production engineers, tool integration, workflows). Data sources are mentioned (Facebook case study with multiple tools, logging infrastructure, work items). However, no specific PM or stochastic technique is formally named; no explicit quality metrics (fitness, precision, etc.) are reported; no validation approach beyond Facebook lessons learned is detailed; and no information on reproducibility (code/data a</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6081,19 +6081,19 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI39" t="b">
         <v>1</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (activity identification and discovery via event log mining). Software engineering context is specified (software development process, jEdit project). Data source is reproducibly named (jEdit project event logs). Specific techniques are formally identified (Word2vec for feature extraction, K-means clustering, silhouette coefficient). Empirical validation is present (practical jEdit case study). However, no discussion of validity threats, no data/code availability stated, and no process model quality metrics (fitness, precision, generalization, etc.) are r</t>
         </is>
       </c>
     </row>
@@ -6237,22 +6237,22 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI40" t="b">
         <v>1</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (forecasting software project delivery and effort using Monte Carlo simulations). SE context explicitly stated (agile projects, user stories, sprints). Data sources described (project historical data, takt time, FTE allocation). Formal technique named (Monte Carlo simulations). Empirical validation with real project data and comparison to developer estimates. Limitations discussed (requirements on input data, accuracy variation with data volume). Quality metrics reported (MMRE: 32%, 20%, 134%). No explicit mention of data/code availability.</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>1</v>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -6399,19 +6399,19 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (understanding student coding processes via process mining). SE context is well-defined (software engineering education/programming training). Process Mining techniques and constructive-synthesizing modeling are named as methods. However, no specific data source is reproducibly described, no empirical validation results are presented in the abstract, no validity threats are discussed, and no quality metrics are reported.</t>
         </is>
       </c>
     </row>
@@ -6552,10 +6552,10 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="n">
         <v>7</v>
@@ -6565,12 +6565,12 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research aim (risk assessment in agile using SPSM), describes SE context (agile methodologies, project management), names data source (JIRA repositories from three open-source projects), specifies stochastic technique (Monte Carlo simulations), validates empirically on real projects, discusses limitations (future work on scaling), and reports process metrics (project duration, issue completion time, effort distributions). However, no mention of code/data availability for reproducibility.</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>1</v>
@@ -6708,28 +6708,28 @@
         <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI43" t="b">
         <v>1</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives stated in abstract (workflow verification and duration prediction). DevOps context explicitly named as SE setting. Non-Markovian Stochastic Petri Nets formally defined. MATLAB simulation case study provides empirical validation. Duration/delay metrics are evaluated. However, no reproducible data source named, no code/dataset availability mentioned, and no threats to validity discussed.</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="n">
         <v>1</v>
@@ -6863,28 +6863,28 @@
         <v>1</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI44" t="b">
         <v>1</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives: evaluate quality of component-based behavior discovery. SE context specified: software execution data/logs and behavioral model discovery. Data source: execution logs from software systems. PM technique: behavioral model discovery (component-based decomposition). Empirical validation through quantitative evaluation of model complexity. Quality metrics: understandability and complexity measures. No explicit discussion of threats to validity or reproducibility/code availability mentioned.</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>1</v>
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -7031,19 +7031,19 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (interactive simulation for process improvement and what-if analysis). Software engineering context is described (process mining, event logs, process discovery, conformance checking). Process trees and simulation techniques are formally named. However, no specific data source is identified, no empirical validation results are presented (abstract only), threats to validity are not discussed, reproducibility is not mentioned, and no quality metrics are reported.</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7187,22 +7187,22 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI46" t="b">
         <v>1</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on improving programmer productivity via task process analysis (QA1). SE context explicitly stated: live projects at CMMI Level 5 company with programmer task execution (QA2). Data source reproducibly described: video screen capture of programmers executing assigned tasks at Robert Bosch Engineering and Business Solutions Limited (QA3). Stochastic technique formally named: Markov chain modeling of task processes (QA4). Empirical validation via case study with real projects and programmer groups (QA5). Limitations and generalizability briefly discussed regarding transfe</t>
         </is>
       </c>
     </row>
@@ -7343,25 +7343,25 @@
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI47" t="b">
         <v>1</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research aim (QA1: analyze efficacy of development process in multidisciplinary teams using process mining). SE context is detailed—agile/scrum in multidisciplinary software development (QA2). Data sources are reproducibly named: Jira and GitHub (QA3). Process-mining technique is formally identified (QA4). Case study on virtual healthcare intervention system provides empirical validation (QA5). Limitations and process deficiencies are discussed (QA6). However, no mention of dataset/code availability or reproducibility artifacts (QA7: 0). No quantitative process model quali</t>
         </is>
       </c>
     </row>
@@ -7486,16 +7486,16 @@
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>1</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -7504,19 +7504,19 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI48" t="b">
         <v>1</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective clearly stated (analyzing CI/CD pipelines for probability of timely delivery). SE context well-described (CI/CD pipelines in modern software development). Stochastic Petri net formally named as technique. Empirical validation via sensitivity analysis demonstrated. However, no specific data source named, no threats to validity discussed, no reproducibility support mentioned, and no formal PM quality metrics (fitness, precision, etc.) explicitly reported—only probability of timely delivery.</t>
         </is>
       </c>
     </row>
@@ -7654,28 +7654,28 @@
         <v>1</v>
       </c>
       <c r="AE49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI49" t="b">
         <v>1</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (process mining analysis and automated effort estimation). SE context is well-defined (agile/Scrum, requirements engineering, virtual healthcare system). Data sources are explicitly named (Jira, GitHub). Process mining technique is mentioned as the core method. Empirical validation occurs via case study application. However, no threats to validity are discussed, no dataset/code availability is mentioned, and no formal quality metrics (fitness, precision, etc.) are reported—only qualitative improvements ('more clear picture', 'mitigated change requests').</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -7766,19 +7766,19 @@
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI50" t="b">
         <v>1</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (identify SDLC process improvements via process mining). SE context explicitly described (software development life cycle in banking sector). Data source identified (Kuveyt Turk Participation Bank's SDLC data). Specific PM technique named (bupaR for process mining discovery). Empirical validation present (real case study with expert evaluation). However, no discussion of limitations/threats, no mention of data/code availability, and no formal quality metrics (fitness, precision, recall, F1) reported.</t>
         </is>
       </c>
     </row>
@@ -7907,13 +7907,13 @@
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>1</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -7932,12 +7932,12 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (process mining to analyze knowledge flows in software development). SE context is named (software development company, process repositories). Process mining techniques are formally mentioned (process discovery, conformance checking, process improvement). Empirical validation exists (experience report from Mexican software company). However, data source origin is not reproducibly described, threats to validity are not discussed, reproducibility materials are not mentioned, and no quality metrics for process models are reported.</t>
         </is>
       </c>
     </row>
@@ -8068,31 +8068,31 @@
         <v>1</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI52" t="b">
         <v>1</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on process mining for software development validation (QA1). Software engineering context is specific: Jira and GitHub in a small development organization (QA2). Data sources are reproducibly named: Jira Issue Tracking System, GitHub version control, and private organizational systems (QA3). Process mining technique is formally identified: discovery and conformance checking across control flow, organizational, case, and time perspectives (QA4). Empirical evaluation is evident through real-data application on an actual software project (QA5). No explicit discussion of v</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
         <v>1</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF53" t="n">
         <v>0</v>
@@ -8239,19 +8239,19 @@
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI53" t="b">
         <v>1</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (three RQs on SDM insights and improvements). SE context is detailed (software development methodologies, tools logs, developer/manager roles). Data source is described (software development tools logs, questionnaires). Process mining is formally named as the technique. Empirical evaluation via single case study confirms QA5. Limitations and generalizability concerns are explicitly discussed (cultural settings, tool availability constraints). However, no dataset or code availability is mentioned, and no quantitative process model quality metrics (fitness,</t>
         </is>
       </c>
     </row>
@@ -8386,10 +8386,10 @@
         <v>1</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on understanding coding behavior via incremental process mining. SE context is explicitly defined (IDE and VCS interactions in academic Java programming). Data source is well-described (customized IDE and VCS event logs from 6 novice students). Incremental process mining technique is formally named. Empirical evaluation conducted on real student programming sessions. However, no specific quality metrics (fitness, precision, etc.) are reported, no explicit discussion of threats/limitations, and no mention of data/code availability.</t>
         </is>
       </c>
     </row>
@@ -8551,25 +8551,25 @@
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI55" t="b">
         <v>1</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective to discover decision-making processes in OSS; SE context explicitly named (Python Enhancement Proposals, OSS governance); data source reproducibly described (1.54 million email messages from Python project); process mining techniques formally named (discovery, visualization, structural analysis); empirical validation through case study with steering council evaluation; limitations discussed (framework extensibility, prior work comparison); however, no metrics like fitness/precision reported and no dataset/code availability stated.</t>
         </is>
       </c>
     </row>
@@ -8704,31 +8704,31 @@
         <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI56" t="b">
         <v>1</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objectives (QA1: liaison between developer activities and software complexity via process mining). SE context is well-defined (QA2: refactoring task, IDE events, 117 developers, 71 teams). Data source is reproducibly described (QA3: IDE work sessions, 320 events collected). Process mining technique is formally named (QA4: process mining methods applied to model processes and extract metrics). Empirical validation is present (QA5: case study with 117 developers, 71 teams classifying refactoring practices). Limitations discussed (QA6: agnostic to language/location mentioned,</t>
         </is>
       </c>
     </row>
@@ -8853,22 +8853,22 @@
         <v>1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>1</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH57" t="n">
         <v>5</v>
@@ -8878,12 +8878,12 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (quantitatively guide CI/CD process quality via probability of timely delivery). Software engineering context explicitly named (CI/CD pipeline, continuous integration, continuous delivery). Stochastic Petri net technique formally identified. Empirical validation demonstrated through sensitivity analysis. However, no specific data source/dataset is named, reproducibility not stated, and threats to validity are not discussed.</t>
         </is>
       </c>
     </row>
@@ -9015,13 +9015,13 @@
         <v>1</v>
       </c>
       <c r="AC58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -9030,19 +9030,19 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI58" t="b">
         <v>1</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (process mining framework for software process insights). Software engineering context explicitly described (version control systems, e-commerce web applications development). Data source identified (version control systems extracting event logs). However, no specific PM technique formally named (ontology-based approach mentioned but not a standard PM algorithm like alpha miner). No validity threats discussed, no reproducibility information provided, and no quality metrics reported.</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB59" t="n">
         <v>1</v>
@@ -9121,31 +9121,31 @@
         <v>1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH59" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objectives (probabilistic resource availability modeling), describes business process simulation context, proposes discovery algorithm from event logs, employs stochastic modeling (probabilistic calendars), includes empirical validation comparing temporal distributions and cycle times, discusses limitations of crisp calendars, and reports quality metrics (temporal distribution replication, cycle time accuracy). Data/code availability not mentioned.</t>
         </is>
       </c>
     </row>
@@ -9280,31 +9280,31 @@
         <v>1</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI60" t="b">
         <v>1</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (analyzing collaboration patterns in GitHub). Software context is well-defined (GitHub repositories, commits, pull requests). Data source is explicitly named (GitHub repositories). Discrete Time Markov Chain is formally specified as the stochastic technique. Empirical evaluation is mentioned via probabilistic temporal logic and model checking. However, no specific threats to validity are discussed, no reproducibility artifacts (dataset/code) are mentioned, and no quantitative process model quality metrics (fitness, precision, etc.) are reported—only qualita</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="AB61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>1</v>
@@ -9442,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -9451,19 +9451,19 @@
         <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives stated (mapping PM techniques to ASD perspectives via literature review). SE context well-defined (Agile, Scrum, XP, event logs). PM techniques explicitly named (discovery, conformance, enhancement). However, this is a literature review without empirical validation on real data, no specific data source is named, no validity threats discussed, no code/data availability mentioned, and no quality metrics reported.</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -9610,19 +9610,19 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objective to develop a mathematical model for probabilistic-temporal analysis of outsourced software development. QA2: Software engineering context explicitly stated ('outsourcing scheme', project complexity, collaboration, methodologies). QA4: Stochastic techniques named (probabilistic transitions, probabilistic distributions, statistical methods). QA3, QA5-QA8: No empirical validation, data sources, reproducibility, or quality metrics reported; appears to be purely conceptual/theoretical modeling without case study or evaluation.</t>
         </is>
       </c>
     </row>
@@ -9754,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="AC63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>1</v>
@@ -9769,19 +9769,19 @@
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI63" t="b">
         <v>1</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research aim to recover developer processes from Jira using process mining (QA1). Software context explicitly stated: maintenance workflows at large company with 74 repositories across 24 teams (QA2). Data source reproducibly described: Jira issues from named industrial partner (QA3). No specific PM technique formally named—only generic process-mining approach mentioned (QA4). Empirical validation through real case study with multiple teams (QA5). Limitations implicitly discussed regarding process deviations and insights (QA6). No mention of code/data availability (QA7). No quality metri</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
         <v>1</v>
       </c>
       <c r="AB64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>1</v>
@@ -9919,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -9928,19 +9928,19 @@
         <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Abstract clearly states research aim (transforming cognitive maps into Markov chains for software projects). QA2: Software development projects explicitly mentioned as context. QA4: Markov chains formally named as the stochastic technique. QA5, QA6, QA7, QA8: No empirical validation, threats to validity, reproducibility data, or quality metrics reported in the abstract; appears to be a conceptual/methodological proposal.</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
         <v>1</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10084,22 +10084,22 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI65" t="b">
         <v>1</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study clearly states research objectives (improving process efficiency in software SMEs via process mining). The SE context is explicitly described (SME software development using L* life cycle model). Data source is identified (event logs from two real projects in the SME). Process mining techniques are named (control flow discovery, conformance checking with time and organization perspectives). Empirical validation via case study of two real projects is present. Threats to validity are discussed (data extraction challenges, communication issues, documentation gaps). Process model quality</t>
         </is>
       </c>
     </row>
@@ -10234,31 +10234,31 @@
         <v>1</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>1</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI66" t="b">
         <v>1</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on RL-based PR outcome prediction. SE context explicitly stated (GitHub, pull-based development, PR review processes). Data source identified as GitHub repositories with PR features and discussions. Markov Decision Processes formally named as stochastic technique. Empirical validation through comparison with baseline models across multiple data splits. Datasets made publicly available for reproducibility. G-mean and performance metrics reported. No explicit discussion of threats to validity or generalizability limitations.</t>
         </is>
       </c>
     </row>
@@ -10393,31 +10393,31 @@
         <v>1</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI67" t="b">
         <v>1</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective to investigate trustworthiness of PR processes via process mining (QA1). Software engineering context is well-defined: OSS development on GitHub with pull request workflows (QA2). Data source is reproducibly described: 17,531 PRs from 18 OSS projects on GitHub (QA3). Process mining technique is formally named: control-flow and semantic anomaly detection with root cause analysis (QA4). Empirical validation through real-data application on GitHub projects (QA5). Limitations discussed regarding project diversity and process variation (QA6). Process quality metrics i</t>
         </is>
       </c>
     </row>
@@ -10549,34 +10549,34 @@
         <v>1</v>
       </c>
       <c r="AC68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI68" t="b">
         <v>1</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on multi-dimensional process analysis of software development (QA1). Software engineering context explicitly stated: GitHub repositories and software development projects (QA2). Data source reproducibly described: GitHub open-source repositories (QA3). No specific PM or stochastic technique formally named (QA4). Empirical evaluation conducted on real data from GitHub (QA5). No discussion of threats to validity or limitations evident (QA6). No mention of data/code availability or reproducibility package (QA7). No process model quality metrics (fitness, precision, recall</t>
         </is>
       </c>
     </row>
@@ -10711,31 +10711,31 @@
         <v>1</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI69" t="b">
         <v>1</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The abstract clearly states research objectives (uncovering temporal dynamics and project behavior via probabilistic model checking). SE context is explicitly GitHub repository analysis with branch management and contributor behavior. Data source is named: GitHub repositories (5 analyzed). Stochastic techniques are formally specified: Discrete-Time Markov Chains and Probabilistic CTL. Empirical validation is present (application to five repositories). However, no threats to validity or limitations are discussed, no data/code availability is mentioned, and no quantitative quality metrics (fitne</t>
         </is>
       </c>
     </row>
@@ -10867,34 +10867,34 @@
         <v>1</v>
       </c>
       <c r="AC70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI70" t="b">
         <v>1</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objectives (comparative analysis of AI vs. traditional repos), describes SE context (GitHub repositories, issues, pull requests), and names data source (eight prominent GitHub projects). However, no specific process mining algorithm is formally named, no quality metrics are reported, threats to validity are not discussed, and no data/code availability is mentioned.</t>
         </is>
       </c>
     </row>
@@ -11020,16 +11020,16 @@
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>1</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH71" t="n">
         <v>5</v>
@@ -11048,12 +11048,12 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objectives stated (bridging GenAI and BPS for what-if scenarios). QA2: No specific SE context named (business process, software development, testing, etc. remain generic). QA3: No data source reproducibly described (no GitHub, Jira, public dataset, or industry partner named). QA4: Specific techniques mentioned (generative models, Business Process Simulation). QA5: Empirical validation present (comparison of methods and evaluation framework applied). QA6: Limitations acknowledged (current approaches fail to capture interdependencies, parameter adjustment challenges). QA7: No</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
         <v>1</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11200,19 +11200,19 @@
         <v>1</v>
       </c>
       <c r="AH72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI72" t="b">
         <v>1</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research aim: automated microservice decomposition via PM+NLP. SE context explicitly stated: monolithic-to-microservices refactoring. Data source: event logs with 6,000 activities each from four applications. PM technique clearly named: inductive mining with NLP integration. Empirical validation on four applications with quality metrics (cohesion, coupling, fitness, precision). Limitations discussed (single vs. multi-dimensional, behavioral insights). No explicit mention of code/data availability. Multiple quality metrics reported (fitness, precision, cohesion, coupling scores).</t>
         </is>
       </c>
     </row>
@@ -11291,31 +11291,31 @@
         <v>1</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI73" t="b">
         <v>1</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objectives (understanding issue resolution processes and their efficiency). SE context is well-defined (OSS development, GitHub repositories, issue handling). Data source is reproducible (GitHub OSS projects, issue event logs). PM techniques are formally named (Direct Follow Graphs, DFG-based entropy calculation, KMeans++ clustering). Empirical validation is present (real-world OSS projects analysis with relationship findings). Limitations and process organization factors are discussed. Quality metrics reported include entropy, issue lifetime, and event transition</t>
         </is>
       </c>
     </row>
@@ -11450,31 +11450,31 @@
         <v>1</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI74" t="b">
         <v>1</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clear (building DT for SDLC). SE context explicitly described (issue-tracking, JIRA, SDLC). Data source named (JIRA issue-tracking systems). Stochastic techniques formally defined (pm4py, Akka actor system, LightGBM). Preliminary empirical validation mentioned. Open-source tools (pm4py, Akka, LightGBM) used. No process quality metrics (fitness, precision, F1) reported; no threats to validity discussed.</t>
         </is>
       </c>
     </row>
@@ -11614,22 +11614,22 @@
         <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI75" t="b">
         <v>1</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (stochastic conformance checking via VLMCs); software context explicitly stated (process mining, software performance engineering); data source named (11 benchmark datasets from PM community); stochastic technique formally defined (Variable-length Markov Chains with uEMSC conformance measure); empirical evaluation on 11 datasets with comparison to 18 SCC techniques; limitations discussed (efficiency, dataset scope); quality metrics reported (uEMSC values, processing times); reproducibility/code availability not mentioned.</t>
         </is>
       </c>
     </row>
@@ -11773,22 +11773,22 @@
         <v>1</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI76" t="b">
         <v>1</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>avaliado</t>
+          <t>avaliado_llm</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research aim (streamlining audits via repository mining), describes SE context (NASA critical software development, version control/issue tracking/CI/CD), identifies data sources (GitHub Copilot project and Kaiaulu tool repositories), formally defines PM technique (Kaiaulu repository mining tool), includes empirical case study validation on real NASA project, discusses compliance metrics and their impact, provides both project and tool GitHub repositories for reproducibility, and reports process compliance metrics as evaluation measures.</t>
         </is>
       </c>
     </row>
@@ -11928,22 +11928,6625 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH77" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives on control-flow anomaly detection via LLMs and conformance checking. SE context specified (software monitoring, source-code instrumentation). Data source identified (ERTMS/ETCS case study). PM technique formally named (conformance checking). Empirical validation through case study with metrics (F1-score 95.957%, AUC 93.669%). Limitations acknowledged regarding domain knowledge and coverage. No explicit mention of data/code availability. Quality metrics reported (F1-score, AUC, coverage %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>9ea592cd</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on bottleneck analysis in SW development using process mining (QA1). SW context explicitly mentioned (IDEs, task management systems, development process) (QA2). Process mining techniques identified (discovery, conformance checking, predictive modeling) with simulation as stochastic method (QA4). Case study empirically evaluates approach (QA5). However, no specific data source origin named despite reference to event logs (QA3). No threats to validity, reproducibility details, or quality metrics mentioned (QA6, QA7, QA8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2c1f1193</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): This is a systematic literature review (SLR) with clear research objectives on process mining for continuous software monitoring. It describes SE context (CI/CD, runtime monitoring) and data sources (event logs from software execution). Process mining is the core technique examined, but as a review paper, it lacks primary empirical validation, validity discussion, reproducible data/code, and reported quality metrics on its own studies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>69029db6</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study applies process mining (discovery algorithms, procedural flow analysis, declarative techniques) to agile software development artifacts with event logs from 3,418 projects; research objective and software context are clearly implicit in the title and prior screening notes. While the data source (event logs) and technique (process mining) are identified, no specific quality metrics (fitness, precision, etc.) are explicitly mentioned in available text, and threats to validity and reproducibility statements are not evident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7f6a881a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
         <v>6</v>
       </c>
-      <c r="AI77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>avaliado</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>QA inferido automaticamente a partir de screening FT e enriquecimento PDF v4.</t>
+      <c r="AI81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study clearly presents two tools (RuM Toolkit, Declare4Py) for declarative process mining in software processes, with explicit SE context (software development), event logs as data source, and named techniques (declarative process mining). Tools/code availability suggests reproducibility. No formal process model quality metrics (fitness, precision, etc.) are mentioned in the screening evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fda7184e</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on using PM to support software evolution (QA1). Software engineering context specified: Electronic Document Management System with administrative procedures (QA2). Data source identified: logs from EDMS administrative procedures (QA3). No specific PM technique formally named (QA4). Empirical case study provided on EDMS (QA5). No process model quality metrics (fitness, precision, etc.) or validity threats discussed (QA6, QA8). Reproducibility not stated (QA7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3430f3d0</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clear (project status prediction using HMMs). SE context is described (software engineering organization, project management). HMM and Baum-Welch algorithm are formally named. Empirical validation is mentioned (tested with project-specific models on real data). However, no specific data source is named (no repository, project names, or dataset identification), no validity threats are discussed, no reproducibility artifacts are mentioned, and no quantitative metrics (accuracy values, precision, recall, RMSE) are reported despite mentioning 'accuracy'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>56342950</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objectives (fault insertion/fixing patterns), describes SE context (Apache projects, developer activities), names data source (twelve Apache projects repositories), formally defines three stochastic techniques (Petri-net, Markov Chain, Hawkes Processes), performs empirical evaluation on real projects with analysis of developer behavior patterns, discusses differences across projects and limitations. No explicit mention of code/data availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>b5ffb64d</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on fork-type characteristics in open-source development. SE context explicitly stated (880 Java projects, action/observation events). Data source named (open-source projects with forks). Process mining explicitly mentioned as technique. Empirical evaluation on real projects. Dataset availability indicated by 'This dataset relates to the paper' statement. No specific process model quality metrics (fitness, precision, recall, F1) reported in abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>6f295ec6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly applies process mining to Git logs (QA1, QA4), with software development course as SE context (QA2). Git repositories are named as data source (QA3), and empirical evaluation in real educational setting is indicated (QA5). However, no threats to validity, reproducibility artifacts, or process model quality metrics (fitness, precision, etc.) are mentioned in the screening summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>c894f613</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study applies process mining to CI/CD workflows with clear SE context (continuous integration/delivery) and event log sources (Apache Kafka integration from heterogeneous CI/CD artifacts). Process mining technique is named; empirical application to real CI/CD monitoring is evident. However, no specific quality metrics (fitness, precision, etc.), threats to validity, or data/code availability are mentioned in the provided information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>9c4cc898</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The title and prior screening clearly state research objectives (extracting process features from event logs for simulation models). Event logs are mentioned as data source. System Dynamics is a named stochastic technique. However, software engineering context is unclear/not stated, threats to validity are not discussed, reproducibility/data availability is not mentioned, and specific PM quality metrics are not reported in the available text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>db43c22c</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Research objective is clear—assessing effectiveness of Agile processes using probabilistic causal models. QA2: SE context is explicitly described (Agile methodology, software development, sprints). QA4: Markov chains are formally named as the mathematical apparatus. QA5: An empirical example of evaluating a software development process within an Agile sprint is presented. QA3, QA6, QA7, QA8: No specific data source is named (no repository, project, or dataset identified); no threats to validity or generalizability discussed; reproducibility not addressed (no code/data availability stated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>f59b10d5</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The title clearly states a research objective (build outcome prediction). SE context is explicit (CI/CD, real software project, repository mining). Data source is identified (version control repository in a real project). However, no specific stochastic/PM technique is named, threats to validity are not discussed, and reproducibility/code availability is not mentioned. Process model quality metrics are implied through build outcome prediction accuracy evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>abfd6b2e</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective of identifying programmer workflow using process mining on commit/collaboration tool event logs. Software context (development team roles), data source (collaboration tools, commit data), and PM technique (process mining workflow discovery) are explicitly named. Quality issues (deadlocks, synchronization problems, etc.) are identified, SEQUAL framework is applied as evaluation metric, and limitations/threats are discussed. However, no mention of dataset/code availability or reproducibility package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>e89188a6</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives clearly stated (agile project tracking via state-space approach). Software engineering context identified (software project management, agile tracking). Monte Carlo simulation explicitly named as stochastic technique. Empirical validation through simulation mentioned. However, no real data source reproducibility, threats to validity discussion, or availability of data/code stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>6e572cbb</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI93" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study has clear PM objective (exploring PM opportunities in educational SE via GitLab analysis), describes SE context (educational software development, repository mining), identifies reproducible data source (GitLab repositories, event logs), and specifies PM technique (Disco tool for process mining). Empirical evaluation is applied to real GitLab data. However, no specific process model quality metrics (fitness, precision, recall) are reported, threats to validity are not discussed, and reproducibility artifacts are not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>6f9a5a08</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The title clearly states a research objective (monitoring software development with process mining). Software engineering context is evident (VCS, issue trackers, software development process). Data sources are identified (software repositories including version control and issue tracking). However, no specific process mining technique is formally named, no empirical validation is mentioned (position paper), threats to validity are not discussed, reproducibility/data availability is not stated, and no quality metrics are reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4409efef</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study has clear objective (predicting bug-fixing time), defined SE context (bug handling in open source project), identifiable data source (Bugzilla Firefox), formal technique (Markov+Monte Carlo), empirical evaluation, and process metrics. Reproducibility inferred from 'open source' and replication study nature. Threats to validity not explicitly mentioned in available text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4082a5b1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly applies process mining (discovery, resource, activity analysis) to seven real software development projects using event logs, establishing research objectives in project management context. Research objectives, SE context (software development), and data source (event logs from real projects) are explicitly stated; process mining techniques are named; empirical evaluation on real project data is confirmed. However, process model quality metrics (fitness, precision, etc.) and validity threats are not mentioned in the screening evidence, and reproducibility/code availability is not</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>223a62e3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objectives (workflow efficiency and sentiment dynamics analysis in repositories). SE context is well-described (GitHub repositories, issues, pull requests). Data source is explicitly named (eight GitHub projects with issues and pull requests). However, no specific process mining technique is formally named (alpha miner, inductive miner, etc.), no quality metrics (fitness, precision, etc.) are reported, threats to validity are not discussed, and data/code availability is not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3ef399e6</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study clearly addresses process mining applications in software engineering (QA1, QA2). Process mining techniques (discovery, conformance checking) are formally identified (QA4), and case studies are mentioned indicating empirical validation (QA5). However, no specific data source is named (QA3), no quality metrics are reported (QA8), reproducibility and validity threats are not discussed (QA6, QA7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4c73b15f</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI99" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (predicting project completion date), software engineering context (agile software projects), data source identified (historical throughput event logs), and Monte Carlo Simulation formally named as the stochastic technique. Empirical validation implied through application to real project data. No explicit metrics reported, threats to validity not mentioned, and data/code availability not stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0a07a816</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives on hierarchical performance analysis for process mining (QA1). Software system processes explicitly mentioned as application domain (QA2). Process mining techniques (discovery, conformance, performance analysis) formally defined (QA4). Implementation and evaluation on software system processes demonstrated (QA5). Performance metrics are introduced but data source not specified (QA3=0), reproducibility/availability not stated (QA7=0), and no discussion of validity threats evident (QA6=0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>63e1f0bf</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (privacy-preserving process mining). Software context (event logs from software execution) and PM technique (alpha algorithm) are explicitly named. Experiments are described, and privacy/generalizability concerns are discussed. However, no specific data source is named, no quality metrics (fitness, precision, etc.) are reported, and reproducibility is not addressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>07ddd290</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI102" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on process verification using PM. SE context explicitly stated (bug, task, defect management in a large IT company). Data sources named (real process data from case studies). PM techniques explicitly mentioned (process mining algorithms). Three case studies provide empirical validation. Open-source EPF Composer tool ensures reproducibility. No quality metrics (fitness, precision, recall, etc.) are reported in the abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>08d64489</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI103" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (discovering collaboration patterns from development logs). Software engineering context identified (large-scale software development, developing logs, software development process). Process mining technique formally named (trace alignment). Empirical evaluation mentioned (experimental results from CPNTools dataset). However, data source lacks specific reproducibility details (no named repository/project), no process model quality metrics reported, no validity threats discussed, and no code/data availability mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>632737fb</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI104" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Paper clearly states objective of applying probabilistic model checking to software processes (QA1). SE context is defined as lean-kanban process in software maintenance (QA2). Markov chain models and probabilistic temporal logic are formally defined techniques (QA4). Real case study validation through PRISM is empirical evidence (QA5). PRISM is open-source software tool mentioned (QA7). However, no specific data source is named for the case study (QA3), no threats/limitations discussed (QA6), and no quantitative process model quality metrics reported (QA8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>7ab40121</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objective stated (software reliability estimation via stochastic methods for automotive release decisions). QA2: Software engineering context specified (automotive software development, quality management, release process). QA4: Stochastic analysis methods explicitly named (stochastic fault rate models, reliability estimation). QA8: Process/performance metrics mentioned (residual error rate, failure performance prediction, KPIs). QA3: No specific data source named. QA5: No empirical validation or case study reported—appears conceptual. QA6: No discussion of limitations or t</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>d4a1d75c</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clearly stated (mining projects from artifacts for compliance verification). SE context is specified (safety-critical projects, documentation, software repositories). Data source is named (software repositories, project-generated artifacts). However, no specific PM/stochastic technique, empirical validation, validity threats, reproducibility information, or quality metrics are mentioned in the abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>b5ea4fdd</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated: modeling software development as Markov random process. SE context explicitly described (software component development at multiple levels). Markov chains formally identified as the stochastic technique. However, no empirical validation, data source, validity threats, reproducibility details, or quality metrics are mentioned—study appears primarily theoretical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>c42be0aa</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study is clearly a review on software process mining using Petri nets (QA1, QA2, QA4 evident from title and prior screening). However, as a review paper, it lacks specific data source description (QA3), empirical validation of its own methods (QA5), explicit discussion of validity threats (QA6), reproducibility artifacts (QA7), and reported quality metrics (QA8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>c149b689</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI109" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (RQs on incident management subprocess impact and metrics). SE context is explicit (incident management in IT services company). Process Mining and BPI techniques are named, and case study provides empirical validation. However, no specific data source origin is named (e.g., tool name, project identifier), no quality metrics (fitness, precision, etc.) are reported, threats to validity are not discussed, and reproducibility resources are not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3d967450</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study has clear objectives (defect prediction modeling), describes SE context (platform-based product lines, development process), uses identifiable data source (defect tracking systems/issue logs), applies Markov chains formally, validates empirically with real data, and reports quality metrics. No threats to validity or data reproducibility information is mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>b8b5b64e</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI111" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective clearly stated (risk prediction in software projects). SE context is specific (defect lifecycle, quality perspective, mobile software projects). Data source identified (software repository). Markov chain is formally named as the stochastic technique. Empirical evaluation conducted on real-industry mobile projects. However, no specific quality metrics (fitness, precision, etc.) are reported in the abstract, threats to validity are not discussed, and data/code availability is not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ee562777</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (mining technique for project-oriented processes from VCS). Software engineering context explicitly stated (large engineering processes, version control systems). Data source identified as VCS. Process mining technique formally defined (project-oriented business process mining algorithm). Empirical evaluation mentioned (prototypical implementation and comparison). No explicit mention of threats to validity, dataset/code availability, or quantitative quality metrics (fitness, precision, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>e23bbc10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI113" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The paper clearly states its aim to introduce a process mining technique for uncovering tailoring candidates (QA1). Software development context is explicitly described (process tailoring, activities, artifacts, control flows) (QA2). Data source is identified as execution logs from a real software development scenario for Brazilian Federal Institutes (QA3). Process mining is formally named as the technique used (QA4), and empirical evaluation on real data is mentioned (QA5). However, no threats to validity or limitations are discussed (QA6), no data/code availability is stated (QA7), and no sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>b7fd840a</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective (task process impact on productivity), specifies SE context (unit-testing at Robert Bosch), identifies data source (18 programmers from 3 live projects), formally defines Markov chains, includes empirical field study evaluation, and reports comparative metrics (Euclidean distance, process similarity). No threats to validity discussion or data availability statement are evident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>261f6383</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI115" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on quantifying economic impact of process change via cycle-time analysis (QA1). Software development process methodology context explicitly stated (QA2). Monte Carlo simulation technique formally named (QA4). Commercial case study demonstrates empirical validation (QA5). Cycle-time performance metric reported as evaluation metric (QA8). However, data source (project/repository) is not reproducibly described (QA3), threats to validity not discussed (QA6), and no mention of dataset/code availability (QA7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>82b3401d</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Abstract clearly states threefold research objectives (conformance, discovery, extension). FLOSS repositories and event logs are named as software engineering context and data source. Process mining techniques (discovery, conformance checking, extension) are explicitly identified. However, no empirical validation results, validity discussion, reproducibility information, or quality metrics are evident in the provided abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2ee3dc10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (Software Process Intelligence framework); software engineering context explicitly described (ITS, VCS, PAIS, software development process); data sources named (Issue Tracking System, Version Control System). However, no specific PM/stochastic technique formally defined, no empirical validation reported, no validity threats discussed, no reproducibility statement, and no process model quality metrics mentioned—this appears to be a position/framework paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>932f2a18</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated: applying process mining to support CMMI-based software process assessment. Software engineering context explicitly described (CMMI, software process improvement, change control process). Real industrial case study of change control board process provides data source and empirical validation. Process mining techniques are formally referenced, and limitations/threats are discussed. However, no specific quality metrics (fitness, precision, etc.) are reported, and no mention of dataset/code availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>508f3b5b</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI119" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (deviation detection in process execution) and SE context (software development process in IT department of automotive company). Data source identified (event logs from real software development process). Process mining techniques and conformance checking are formally named. Empirical validation via case study on real process logs. No threats to validity, data availability, or process model quality metrics (fitness, precision) are explicitly mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>f6edde4a</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective: framework for OSS reliability assessment via simulation (QA1). SE context: debugging/testing activities in OSS projects, specifically Apache and GNOME (QA2). Data source: three real datasets from Apache and GNOME projects explicitly named (QA3). Stochastic technique: rate-based queueing simulation model formally defined (QA4). Empirical validation: real data application from Apache and GNOME with results showing framework effectiveness (QA5). Threats discussed via characterization of differences between OSS and CSS debugging (QA6). No mention of dataset/code availabil</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1363926c</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Research objective is clearly stated (predicting OSS release dates). QA2: Software context is specified (open source software development). QA4: Stochastic technique is named (Generalized Software Reliability Model/GSRM based on stochastic process). QA3, QA5, QA6, QA7, QA8: Abstract provides no information on specific data sources, empirical validation method, validity threats, reproducibility, or reported metrics—only abstract available with insufficient detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>d1ed6154</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI122" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The abstract clearly states research objectives (discover runtime process, identify inefficiencies, enhance process capabilities via process mining). Software engineering context is explicit (issue tracking, code review, software repositories). Data sources are named (software repositories, project data). Process mining techniques are formally identified (discovery, conformance verification, performance analysis using ProM and Disco tools). However, no empirical validation results, threats to validity, reproducible datasets/code, or quality metrics (fitness, precision, recall, F1) are reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>829f8c13</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study clearly states objectives (discovering runtime process maps, inefficiencies, inconsistencies), describes SE context (issue tracking/bug management), names data source (Bugzilla Firefox), defines PM techniques (process discovery, conformance checking, performance analysis), includes empirical case study, discusses process conformance metrics, and mentions limitations implicitly through methodology description. Data/code availability is not stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2647ea07</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI124" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective of software process verification using process mining (QA1). SE context is detailed: bug/task/defect management processes in a large IT company (QA2). Data source is real process data from case studies, including a named industry partner (QA3). Process mining and conformance checking techniques are explicitly named (QA4). Three empirical case studies with real data provide validation (QA5). Open-source EPF Composer tool and custom plugin are mentioned, indicating reproducibility infrastructure (QA7). Verification against process models implies quality metrics, th</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ad250ae5</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (intentional process model discovery from logs), software engineering context (Eclipse platform usage), stochastic technique (Hidden Markov Models), data source (Eclipse platform activity logs), empirical validation (case study), and quality metrics (precision-fitness metric). No threats to validity discussion or explicit data/code availability mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ceec0a17</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clear: process conformance checking via CSP. Software context (process-aware information systems) is described. CSP and FDR model checker are formally named techniques. However, no empirical validation, specific data source, quality metrics, or reproducibility information is mentioned in the abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>e454d548</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (process verification using PM); specific SE context (bug, task, defect management processes); reproducible data source (real process data from IT company case studies); process mining technique explicitly named; empirical validation via three case studies; open-source EPF Composer tool used (reproducibility). However, no quality metrics (fitness, precision, recall, etc.) are reported, and threats to validity are not discussed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>3231578f</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives clearly stated (process mining for defect resolution). SE context explicitly detailed (ITS, PCR, VCS repositories in Google Chromium). Data sources named (three repositories; Google Chromium project; event log created with caseID, timestamp, activity, performer). PM technique formally defined (Disco tool for process discovery). Empirical validation present (case study on real Google Chromium project with bottleneck and anti-pattern analysis). Process model quality metrics reported (handover of work, subcontracting, joint cases/activities, performance analysis). No threats t</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>326da20f</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objective stated (proposing a stochastic simulation model for risk management). QA2: Software engineering context clearly identified as 'software project risk management process'. QA4: Although stochastic simulation is mentioned, no specific technique (e.g., Monte Carlo, Markov chains) is formally named in the abstract. QA5: Validation is mentioned ('we also validate our simulation model'), indicating empirical evaluation. QA3, QA6, QA7, QA8: No data source, specific stochastic technique, reproducibility details, or quality metrics are described in the abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>9249c6bb</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objective stated—conformance checking of event logs against reference processes. QA4: CSP (Communicating Sequential Processes) and PAT toolkit formally named. QA8: Conformance metrics explicitly mentioned (fitness, closeness, appropriateness). QA2, QA3, QA5, QA6, QA7 all score 0 due to lack of specific SE context, reproducible data source, empirical validation beyond illustration, validity discussion, and availability statement in abstract alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>9a84a55d</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The paper clearly states its objective: adapting a correlation algorithm to extract event logs from non-process-aware systems (QA1). The SE context is described—source code instrumentation for event collection from traditional systems (QA2). However, no specific data source is named (QA3), no formal PM or stochastic technique is identified by name (QA4), and while a case study validates the approach (QA5), no process model quality metrics or validity threats are reported (QA6, QA8), and reproducibility resources are not mentioned (QA7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>c9cdb64d</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI132" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Title and prior screening confirm explicit case study of process mining applied to software development and testing with event logs and ProM framework (Alpha, Heuristic Mining algorithms). SE context, data source, and PM technique are clearly described. Empirical evaluation via case study is evident. No abstract limits QA1-8 assessment, but full-text screening indicates these elements are present except threats to validity discussion and quality metrics reporting are not mentioned in screening summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>51b4ae2b</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI133" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on performance prediction (QA1). SE context specified: software development teams in IT company with multiple sites (QA2). SAN formally defined as technique (QA4). Empirical case study with actual project observations validates the model (QA5). However, data source (project/company) is not reproducibly named (QA3), no specific quality metrics (fitness, precision, etc.) are reported (QA8), threats to validity not discussed (QA6), and reproducibility/code availability not mentioned (QA7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>917d9592</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objective stated—mapping FTS characteristics to stochastic models to predict performance indices. QA2: Specific SE context described (Follow-the-Sun, globally distributed software development, team handoffs). QA4: Stochastic modeling technique explicitly mentioned as the formal approach. QA5, QA8: No empirical validation or evaluation metrics reported—purely conceptual mapping. QA3, QA6, QA7: No data source, reproducibility, or threat discussion evident in abstract/provided text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4316248d</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI135" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective clearly stated (conformance analysis using process mining in SW development). SE context specified (software maintenance project, development environments). Data source named (activity records from software maintenance project, event logs from management tools). PM technique explicitly mentioned (process mining, conformance analysis). Empirical validation via exploratory case study on real project. Process model quality metrics implicit in conformance checking. No availability of data/code stated, and threats to validity not discussed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ae20e68e</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated: mining organizational models from non-invasive data in software companies. Software engineering context is explicitly named (software company, development processes). However, the specific data source is not reproducibly described, no formal PM/stochastic technique is named, threats to validity are not discussed, reproducibility/code availability not mentioned, and no quality metrics are reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>c24db118</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr"/>
+      <c r="Z137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated: extract realistic process models from development project data and improve CCB process understanding. SE context clearly identified (Change Control Board process, large industrial company in The Netherlands, software development). Process mining technique is formally named and defined as the approach. Case study empirically applies process mining to real industrial data. However, no specific validity threats discussed, no dataset/code availability mentioned, and no quantitative quality metrics (fitness, precision, etc.) are reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>f449ac41</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr"/>
+      <c r="Z138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Title clearly states research objectives (conformance checking via process mining). Software development processes context is explicit in the title. However, without the full text or abstract, data source reproducibility cannot be verified, empirical validation is not evident, validity threats are not discussed, reproducibility materials are not mentioned, and specific quality metrics are not reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>e856dbe4</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI139" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clear: extracting software process metrics from repositories. SE context is specified (bug tracker, configuration management event log, project management). Data source is described (large industry project repository over several years). However, no specific stochastic/PM technique is named, no threats to validity discussed, and reproducibility/data availability not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ee5ccaa2</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI140" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLM-scored (claude-haiku-4-5-20251001): QA1: Research objective is clear—discover shortcomings in Change Control Board process and determine improvements. QA2: Software engineering context explicitly stated (software development process improvement, Change Control Board). QA4: Process mining techniques are named as the formal approach. QA5: Application is described as empirical case study in an organization during a real software development project. QA3, QA6, QA7, QA8: No specific data source naming (organization, dataset, or repository not identified); no threats to validity or reproducibility discussion; no process model quality </t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>7e6b3f9f</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective (process mining in software maintenance context). Software engineering context is explicit (maintenance project, software metrics, software operation). However, specific PM technique is not named, data source origin is vague ('metrics data from a software maintenance project' with no named system/repository), no quality metrics reported, and no discussion of threats to validity or reproducibility details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>fcc830f6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI142" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states research objective (asymptotic stability model for distributed outsourced IT R&amp;D projects). SE context is explicit (multicomponent distributed outsourced software development). Data source is identifiable (observational data from actual industrial projects). Stochastic technique is formally named (empirical production functions, stochastic distributions, Monte Carlo simulations). Empirical validation via comparison of simulations with real industrial project data is present. Threats discussed (departure from linearity causes). Model quality assessment through simulation do</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>266210a7</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI143" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (simulation model for process-centered SE environments with sensitivity analysis). SE context explicitly mentioned (PSEE database, project management, software development processes). Stochastic technique named (simulation with deterministic/stochastic data manipulation). Real case study provides empirical validation. However, no specific data source details (repository/project names), no process model quality metrics reported (fitness, precision, etc.), no threats to validity discussed, and no mention of data/code availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ba2ff831</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI144" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study proposes a stochastic renewal model for bug patching optimization with clear SE context (software defect lifecycle). Real vulnerability data (Nimda, Debian) provides empirical validation and a named data source. However, no abstract limits QA1 confidence, no specific process quality metrics (fitness, precision, F1, etc.) are mentioned, reproducibility/threats to validity are not stated in the screening text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ae4f4926</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI145" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective clearly stated (uncertainty management in software development). SE context explicitly described (software development process, risk management). Stochastic techniques formally defined (generalized stochastic Petri net, Markov process algorithm). Real-world case study provided for empirical validation. However, data source not reproducibly described, no process model quality metrics (fitness, precision, etc.) reported, no discussion of validity threats, and reproducibility/code availability not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>be942093</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI146" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The study clearly states objectives in discovering and modeling OSS development processes (NetBeans case study) with detailed SE context (software development, repository mining). Data sources are explicitly described (event logs, version control, project artifacts). However, no formal stochastic/PM technique is named, quality metrics are not reported, threats to validity are not discussed, and reproducibility/data availability is not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>d7b22f54</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Research objective clearly stated (quantitative analysis of VBSPs using DB-SOPN). QA2: Software engineering context explicitly described (value-based software processes, software process lifecycle, stakeholder perspectives, policy comparison). QA4: Specific stochastic technique formally named (Decision-Based Stochastic Object Petri Nets). QA3, QA5, QA6, QA7, QA8: No empirical evaluation case study or experiment mentioned, no data source specified, no threats to validity discussed, no reproducibility statement, and no quality metrics (fitness, precision, recall, etc.) reported—appears to b</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ddeca0e6</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI148" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective to evaluate conformance metrics on noisy data; describes SE context (XP teams developing software); identifies data source (14 teams recording project events); names formal technique (Rozinat and Aalst conformance metrics, fitness); includes empirical case study validation; discusses limitations (metrics ineffectiveness on noisy data); reports quality metrics (fitness and appropriateness values); does not mention data/code availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>3ddbfd94</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLM-scored (claude-haiku-4-5-20251001): QA1: Abstract clearly states research objectives (process mining framework for software processes). QA2: Software engineering context is detailed (SCM systems, software configuration management, software development processes). QA3: Data source is described (SCM systems, which collect process information from software engineering activities). QA4-QA8: No evidence provided—the abstract mentions a framework and algorithmic approach but does not name specific PM techniques (alpha miner, inductive miner, etc.), report empirical validation, discuss validity threats, mention reproducible data/code, </t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>e9a40e7a</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI150" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Research objective (economic impact prediction) is clear. QA2: Software development process context explicitly mentioned (BMW real-world setting). QA4: Absorbing Markov chains formally identified as the stochastic technique. QA5: Empirical validation via real industrial case study (BMW) confirmed. QA3, QA7: Data source origin (BMW project details) not reproducibly described or made available. QA6: No threats to validity mentioned. QA8: No process quality metrics (fitness, precision, etc.) reported in the screening rationale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>cdf1f104</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives on process recovery for software process improvement (QA1). Software development context specified as a small organization (QA2). Empirical data collected and pilot case study conducted (QA5). However, no specific data source is named (QA3), no formal PM/stochastic technique is identified (QA4), no quality metrics are reported (QA8), threats to validity not discussed (QA6), and reproducibility information absent (QA7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2c280053</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
+      <c r="Y152" t="inlineStr"/>
+      <c r="Z152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI152" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly addresses process discovery and modeling in OSSD (QA1, QA2). Data source is explicitly identified as public repositories and software artifacts (QA3). Process mining and simulation techniques are mentioned as core methods (QA4). Empirical evaluation is indicated by "reenacting" processes and analyzing real open-source projects (QA5). No abstract available limiting visibility of validity discussions and quality metrics; no mention of reproducibility artifacts or specific evaluation metrics (QA6, QA7, QA8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>40bc718e</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The abstract clearly states the research objective (quantifying economic benefit of process variations). Software engineering context is described (test/development environments, development process). Absorbing Markov chains are formally defined as the stochastic technique. Empirical validation is present (large-scale commercial organization case study). Process model quality is addressed through effort/duration prediction metrics. However, data source reproducibility and threats to validity are not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>9c255853</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI154" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives on empirical issues in software process simulation modeling (QA1). SE context explicitly stated: software development, process improvements, project management (QA2). Stochastic technique formally named: Monte Carlo simulation (QA4). Empirical validation through practical field work applications (QA5). Threats/limitations discussed: small sample sizes, variability, outliers, loosely defined metrics (QA6). Quality metrics mentioned: verification, validation, financial performance measures (NPV, DEA) (QA8). Data source reproducibility and code availability not stated (Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>96767878</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Title clearly names a stochastic technique (non-homogeneous continuous-time Markov chain) satisfying QA4, but absence of abstract prevents verification of research objectives (QA1), SE context specificity (QA2), data source reproducibility (QA3), empirical validation (QA5), validity discussion (QA6), reproducibility (QA7), and quality metrics (QA8). Full-text review is required to assess these criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>07e55287</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI156" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on automated process discovery from event data (QA1). Software process engineering context explicitly stated (QA2). Markov method and additional stochastic techniques formally named (QA4). Industrial case study mentioned indicating empirical validation (QA5). However, specific data source/repository not named (QA3), no explicit discussion of validity threats (QA6), reproducibility not addressed (QA7), and no quantitative quality metrics reported (QA8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>a20e7c58</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective is clear (modeling defect removal effectiveness in distributed development with code churn). Software engineering context is well-defined (distributed development, testing, code churn dynamics). Monte Carlo simulation is explicitly named as the stochastic technique. Empirical validation occurs through process simulation. However, data source is simulated/synthetic (no real repository or dataset named), no explicit discussion of validity threats, and no mention of reproducible artifacts or code availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>3c810db6</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective on software scheduling via process modeling (QA1). Software engineering context explicitly stated: software project development, scheduling, and rework (QA2). MDP (Markov decision process) formally defined as the stochastic technique (QA4). Empirical evaluation demonstrated through sample projects with computed optimal strategies (QA5). However, no specific data source named (QA3=0), no quality metrics like fitness/precision reported (QA8=0), no reproducibility package mentioned (QA7=0), and no validity threats discussed (QA6=0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>be899615</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives are clearly stated (extracting collaboration models from VCS logs). Software context is explicitly described (version control system logs, developer collaboration). Data source is reproducible (real-life VCS logs are mentioned). Fuzzy mining algorithm is formally named as the PM technique. Empirical validation is provided (demonstration on real-life VCS log). However, threats to validity are not discussed, dataset/code availability is not mentioned, and no quantitative process model quality metrics (fitness, precision, etc.) are reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ec38f0ba</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI160" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objectives clearly stated (extracting test cases from production event logs using process mining). Software context well-defined (executable business processes, production systems, development/testing). Process mining techniques and event logs named as data source. However, no empirical validation results reported, no threats to validity discussed, no reproducibility/code sharing mentioned, and no quality metrics (fitness, precision, etc.) reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2e76e921</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear aim stated (explore usability of process mining in agile development). QA2: Specific SE context identified (Scrum, agile software development). QA5: Exploratory case study on a software project is described. QA3-4: No specific data source (event log origin) or formal PM technique names (e.g., alpha miner, inductive miner) are explicitly stated. QA6-8: No discussion of threats to validity or quality metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>0d31db29</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI162" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Research objective clearly stated (applying process mining to SCAMPI process appraisals). SE context well-defined (software process assessments, SCAMPI maturity framework). Process mining techniques named as core method. Two case studies performed providing empirical validation. Limitations of current methods explicitly discussed as threats. However, no specific data source named, no quality metrics (fitness, precision, etc.) reported, and reproducibility not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>16e31373</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Study clearly states objective of discovering software process lines from logs (QA1). Software engineering context is explicit: software projects at Mobius company (QA2). Data source is reproducibly described: project events from Mobius, a Chilean software company (QA3). Specific PM technique named: v-algorithm with threshold-based clustering (QA4). Empirical validation performed on real company data (QA5). Discusses threshold effects on discovery quality dimensions, extending metrics (QA6). No mention of dataset/code availability (QA7=0). Process quality metrics discussed: fitness, precision,</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>37b22a16</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Research objective clearly stated—developing a framework for Process Mining techniques in Software Process Lines. QA2: Software engineering context explicitly described—software development domain and process variants. QA3-8: This is a research proposal/position paper with no data source, formal technique definition, empirical validation, quality metrics, reproducibility details, or threat discussion provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>f356af5c</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective: predict release dates in agile/OSS using reliability models. SE context explicitly stated: agile development and open source software. Data source identified: OSS projects with issue/fault detection data. Stochastic technique named: Generalized Software Reliability Model (GSRM) based on stochastic process. Empirical evaluation: applied to OSS with error rate metric (0.572% best case). Quality metric reported: Error Rate. Threats to validity and data availability not mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>fa561e12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI166" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): The paper clearly states research objective: discovering Software Process Lines (SPrL) from project logs. It describes SE context (software process definition, project logs) and names a specific data source (Mobius company project log). The v-algorithm is formally proposed as a process mining technique using thresholds to distinguish base/variable/noise relations. Empirical validation occurs via case study on real company data with identified process insights. However, no threats to validity are discussed, no reproducibility artifacts or datasets are mentioned, and no quantitative quality metr</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>53d897a8</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objectives on discovering functional architecture from event logs using process discovery (QA1). Software engineering context explicitly stated: functional architecture decomposition, component behavior, and workflow modeling (QA2). Data sources named: event logs and message sequence charts (QA3). Process discovery technique formally identified as the core approach (QA4). Empirical validation through running example of payment system (QA5). No threats to validity or limitations discussion evident (QA6). No mention of dataset availability or reproducibility package (QA7). No proc</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>6fd30d7e</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI168" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): Clear research objective stated (mining process data from student repositories to provide learning analytics). SE context well-described (undergraduate course, team-based projects, three repositories: wiki, VCS, issue tracking). Data source reproducibly described (19 student teams, 5 members each, three repository types). However, no specific PM technique formally named (alpha miner, inductive miner, etc.—only 'process mining' mentioned generically). Empirical validation present (real data analysis of 19 teams). Limitations and challenges discussed. Code/data availability not mentioned. Multip</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>84315802</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Clear research objective to develop stochastic models and Monte Carlo simulation for effort estimation. QA2: SE context explicitly stated (software project life cycle phases, effort estimation, outsourcing organization). QA4: Monte Carlo simulation technique formally named. QA5: Empirical validation in mid-sized software services outsourcing organization. QA3, QA7: No reproducible data source or code/dataset availability mentioned. QA6: No threats to validity discussed. QA8: No process model quality metrics (fitness, precision, etc.) reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>0fcd5ece</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>avaliado_llm</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>LLM-scored (claude-haiku-4-5-20251001): QA1: Research objectives clearly stated (process improvement diagnosis and simulation of software development). QA2: Software engineering context is described (software development process, process improvement, process diagnosis). QA4: Stochastic technique formally named (Monte Carlo simulation). QA3-QA8: No evidence in abstract of specific data sources, empirical validation, validity discussion, reproducibility resources, or quality metrics reported.</t>
         </is>
       </c>
     </row>
